--- a/test/configs/data/develop/stochastic_base.xlsx
+++ b/test/configs/data/develop/stochastic_base.xlsx
@@ -1201,7 +1201,7 @@
     <col min="19" max="19" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15" style="8" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="26" max="32" width="13.5546875" style="6" bestFit="1" customWidth="1"/>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>30</v>
       </c>
       <c r="H2" s="4">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="I2" s="4">
         <v>725545.55299179</v>
@@ -1392,7 +1392,7 @@
         <v>35</v>
       </c>
       <c r="W2" s="4">
-        <v>55</v>
+        <v>0.01</v>
       </c>
       <c r="X2" s="2">
         <v>1</v>
